--- a/src/Docu/ostc_hardware_string.xlsx
+++ b/src/Docu/ostc_hardware_string.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">HW_descriptor</t>
   </si>
@@ -31,13 +31,19 @@
     <t xml:space="preserve">SW_CONF</t>
   </si>
   <si>
-    <t xml:space="preserve">C9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">← Enter here</t>
+    <t xml:space="preserve">HW_variants2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HW_variants3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Enter here in HEX</t>
   </si>
 </sst>
 </file>
@@ -54,6 +60,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -75,12 +82,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -131,45 +140,41 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -244,94 +249,236 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>5</v>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(A2)+256)),9,1)="1")),"Battery gauge available","")</f>
         <v>Battery gauge available</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),9,1)="1")),"Display Typ 1","")</f>
-        <v>Display Typ 1</v>
-      </c>
-      <c r="C4" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C4" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),9,1)="1")),"Screendump included","")</f>
         <v/>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),9,1)="1")),"MS5583 Sensor","")</f>
+        <v>MS5583 Sensor</v>
+      </c>
+      <c r="E4" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),9,1)="1")),"Dual Comm","")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="str">
+      <c r="A5" s="6" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(A2)+256)),8,1)="1")),"Ambient light sensor found","")</f>
-        <v>Ambient light sensor found</v>
-      </c>
-      <c r="B5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="B5" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),8,1)="1")),"Display Typ 2","")</f>
         <v/>
       </c>
-      <c r="C5" s="6" t="str">
+      <c r="C5" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),8,1)="1")),"Compass included","")</f>
         <v>Compass included</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),8,1)="1")),"Less IO CPU","")</f>
+        <v/>
+      </c>
+      <c r="E5" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),8,1)="1")),"Adjustable Buttons","")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(A2)+256)),7,1)="1")),"Analog O2 input","")</f>
         <v/>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),7,1)="1")),"Display Typ 3","")</f>
         <v/>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),7,1)="1")),"RX functions included","")</f>
         <v/>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),7,1)="1")),"Display Typ 4","")</f>
+        <v/>
+      </c>
+      <c r="E6" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),7,1)="1")),"BLE Only","")</f>
+        <v>BLE Only</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="str">
@@ -340,43 +487,64 @@
       </c>
       <c r="B7" s="7" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),6,1)="1")),"Compass Typ 1","")</f>
-        <v>Compass Typ 1</v>
+        <v/>
       </c>
       <c r="C7" s="7" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),6,1)="1")),"RX update included","")</f>
         <v/>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="7" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),6,1)="1")),"DN flag","")</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),6,1)="1")),"unused","")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="str">
+      <c r="A8" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(A2)+256)),5,1)="1")),"BLE/Bluetooth available","")</f>
         <v>BLE/Bluetooth available</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),5,1)="1")),"Compass Typ 2","")</f>
-        <v/>
-      </c>
-      <c r="C8" s="6" t="str">
+        <v>Compass Typ 2</v>
+      </c>
+      <c r="C8" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),5,1)="1")),"Trimix included","")</f>
         <v>Trimix included</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),5,1)="1")),"Display Typ 5","")</f>
+        <v>Display Typ 5</v>
+      </c>
+      <c r="E8" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),5,1)="1")),"unused","")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="str">
+      <c r="A9" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(A2)+256)),4,1)="1")),"OSTC RX Hardware","")</f>
         <v/>
       </c>
-      <c r="B9" s="6" t="str">
+      <c r="B9" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),4,1)="1")),"Compass Typ 3","")</f>
         <v/>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C9" s="5" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),4,1)="1")),"ccr/pscr included","")</f>
         <v>ccr/pscr included</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),4,1)="1")),"Compass Typ 0","")</f>
+        <v/>
+      </c>
+      <c r="E9" s="5" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),4,1)="1")),"unused","")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="str">
@@ -385,11 +553,19 @@
       </c>
       <c r="B10" s="8" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(B2)+256)),3,1)="1")),"Analog switches available","")</f>
-        <v>Analog switches available</v>
+        <v/>
       </c>
       <c r="C10" s="8" t="str">
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),3,1)="1")),"external sensor included","")</f>
-        <v>external sensor included</v>
+        <v/>
+      </c>
+      <c r="D10" s="8" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),3,1)="1")),"Compass Present","")</f>
+        <v>Compass Present</v>
+      </c>
+      <c r="E10" s="8" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),3,1)="1")),"unused","")</f>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,7 +581,14 @@
         <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(C2)+256)),2,1)="1")),"Cave mode included","")</f>
         <v>Cave mode included</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(D2)+256)),2,1)="1")),"LTC2959 Byattery Monitor","")</f>
+        <v>LTC2959 Byattery Monitor</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <f aca="false">IF(((MID((DEC2BIN(HEX2DEC(E2)+256)),2,1)="1")),"Cave mode included","")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8"/>
@@ -425,7 +608,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
